--- a/artfynd/A 39708-2024 artfynd.xlsx
+++ b/artfynd/A 39708-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104441786</v>
+        <v>135221057</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalvmyrbäcken, S om, Mpd</t>
+          <t>Kalvmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552985</v>
+        <v>553017</v>
       </c>
       <c r="R2" t="n">
-        <v>6946397</v>
+        <v>6946517</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,43 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>2 substratenheter # förrötade granlågor</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95865352</v>
+        <v>135221058</v>
       </c>
       <c r="B3" t="n">
-        <v>83307</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552823</v>
+        <v>553003</v>
       </c>
       <c r="R3" t="n">
-        <v>6946446</v>
+        <v>6946450</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,26 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95865357</v>
+        <v>104441786</v>
       </c>
       <c r="B4" t="n">
-        <v>83307</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalvmyrbäcken, Mpd</t>
+          <t>Kalvmyrbäcken, S om, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553021</v>
+        <v>552985</v>
       </c>
       <c r="R4" t="n">
-        <v>6946481</v>
+        <v>6946397</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,23 +970,1774 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fuktig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2 substratenheter # förrötade granlågor</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135221062</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>553013</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6946422</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135221066</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552980</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6946395</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135221065</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552982</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6946399</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135221055</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>553041</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6946517</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135221059</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>553023</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6946436</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135221064</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552987</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6946406</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135221070</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552828</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6946315</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135221086</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83341</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552835</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6946377</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95865352</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552823</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6946446</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95865357</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>553021</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6946481</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135221067</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>552986</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6946315</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135221087</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552878</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6946380</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135221063</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>553016</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6946417</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hela stammen är full med årsfärska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135221068</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>552861</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6946310</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135221056</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553017</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6946515</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135221069</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>552839</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6946312</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39708-2024 artfynd.xlsx
+++ b/artfynd/A 39708-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221057</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221058</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441786</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221062</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221066</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221055</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221059</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221064</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1749,6 +1799,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221070</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1856,6 +1911,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221086</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95865352</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95865357</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221067</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221087</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,6 +2472,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221063</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2512,6 +2597,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221068</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2631,6 +2721,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221056</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2738,8 +2833,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 39708-2024 artfynd.xlsx
+++ b/artfynd/A 39708-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135221057</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135221058</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135221062</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135221066</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>135221065</v>
       </c>
       <c r="B7" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>135221055</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>135221059</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>135221064</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>135221070</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135221086</v>
       </c>
       <c r="B12" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135221067</v>
       </c>
       <c r="B15" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135221087</v>
       </c>
       <c r="B16" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135221063</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135221068</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>135221056</v>
       </c>
       <c r="B19" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>135221069</v>
       </c>
       <c r="B20" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 39708-2024 artfynd.xlsx
+++ b/artfynd/A 39708-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135221057</v>
       </c>
       <c r="B2" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135221058</v>
       </c>
       <c r="B3" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135221062</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135221066</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>135221065</v>
       </c>
       <c r="B7" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>135221055</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>135221059</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>135221064</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>135221070</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135221086</v>
       </c>
       <c r="B12" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135221067</v>
       </c>
       <c r="B15" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135221087</v>
       </c>
       <c r="B16" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>135221069</v>
       </c>
       <c r="B20" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 39708-2024 artfynd.xlsx
+++ b/artfynd/A 39708-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104441786</v>
+        <v>135221057</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>83420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalvmyrbäcken, S om, Mpd</t>
+          <t>Kalvmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552985</v>
+        <v>553017</v>
       </c>
       <c r="R2" t="n">
-        <v>6946397</v>
+        <v>6946517</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,48 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>2 substratenheter # förrötade granlågor</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104441786</t>
+          <t>https://artportalen.se/Sighting/135221057</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95865352</v>
+        <v>135221058</v>
       </c>
       <c r="B3" t="n">
-        <v>83307</v>
+        <v>83420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552823</v>
+        <v>553003</v>
       </c>
       <c r="R3" t="n">
-        <v>6946446</v>
+        <v>6946450</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,31 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95865352</t>
+          <t>https://artportalen.se/Sighting/135221058</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95865357</v>
+        <v>104441786</v>
       </c>
       <c r="B4" t="n">
-        <v>83307</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalvmyrbäcken, Mpd</t>
+          <t>Kalvmyrbäcken, S om, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553021</v>
+        <v>552985</v>
       </c>
       <c r="R4" t="n">
-        <v>6946481</v>
+        <v>6946397</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,26 +985,1857 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fuktig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2 substratenheter # förrötade granlågor</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441786</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135221062</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>553013</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6946422</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221062</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135221066</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552980</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6946395</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221066</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135221065</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552982</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6946399</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221065</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135221055</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>553041</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6946517</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221055</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135221059</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>553023</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6946436</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221059</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135221064</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552987</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6946406</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221064</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135221070</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552828</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6946315</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221070</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135221086</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83411</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552835</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6946377</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221086</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95865352</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552823</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6946446</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95865352</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95865357</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>553021</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6946481</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/95865357</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135221067</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>552986</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6946315</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221067</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135221087</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552878</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6946380</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221087</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135221063</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>553016</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6946417</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hela stammen är full med årsfärska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221063</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135221068</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>552861</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6946310</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221068</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135221056</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553017</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6946515</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221056</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135221069</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>552839</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6946312</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221069</t>
         </is>
       </c>
     </row>
@@ -1014,6 +2844,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39708-2024 artfynd.xlsx
+++ b/artfynd/A 39708-2024 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135221062</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135221066</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>135221065</v>
       </c>
       <c r="B7" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>135221069</v>
       </c>
       <c r="B20" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
